--- a/data/sars/pacific/tables/Pacific_2018_Appendix2.xlsx
+++ b/data/sars/pacific/tables/Pacific_2018_Appendix2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5264DEC-9B38-1C49-9BD0-4DA6DAEFB99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3460981-566F-444D-B83A-F2F474B2CC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="500" windowWidth="34220" windowHeight="19960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="135">
   <si>
     <t>California Sea Lion (U.S.)</t>
   </si>
@@ -412,10 +412,22 @@
     <t>survey3</t>
   </si>
   <si>
-    <t>revised</t>
-  </si>
-  <si>
     <t>rf</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>RF=0.2 in SAR; RF=0.1 was typo in table</t>
+  </si>
+  <si>
+    <t>revision_yr</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -426,7 +438,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -443,6 +455,12 @@
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -470,7 +488,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -518,6 +536,9 @@
     </xf>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -823,7 +844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:P88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="70.19921875" style="2" bestFit="1" customWidth="1"/>
@@ -837,11 +858,12 @@
     <col min="9" max="9" width="14.19921875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.3984375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="14.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="14" max="15" width="12.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="40.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>117</v>
       </c>
@@ -858,7 +880,7 @@
         <v>121</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>122</v>
@@ -882,10 +904,16 @@
         <v>128</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+        <v>132</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -928,8 +956,11 @@
       <c r="N2" s="8">
         <v>2018</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O2" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -972,8 +1003,9 @@
       <c r="N3" s="11">
         <v>2014</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O3" s="11"/>
+    </row>
+    <row r="4" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1012,8 +1044,9 @@
       <c r="N4" s="11">
         <v>2013</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O4" s="11"/>
+    </row>
+    <row r="5" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1052,8 +1085,9 @@
       <c r="N5" s="11">
         <v>2013</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O5" s="11"/>
+    </row>
+    <row r="6" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1092,8 +1126,9 @@
       <c r="N6" s="11">
         <v>2013</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O6" s="11"/>
+    </row>
+    <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -1132,8 +1167,9 @@
       <c r="N7" s="11">
         <v>2013</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O7" s="11"/>
+    </row>
+    <row r="8" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -1176,8 +1212,9 @@
       <c r="N8" s="11">
         <v>2014</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O8" s="11"/>
+    </row>
+    <row r="9" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
@@ -1220,8 +1257,9 @@
       <c r="N9" s="11">
         <v>2016</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O9" s="11"/>
+    </row>
+    <row r="10" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -1264,8 +1302,9 @@
       <c r="N10" s="11">
         <v>2015</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O10" s="11"/>
+    </row>
+    <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
@@ -1308,8 +1347,11 @@
       <c r="N11" s="8">
         <v>2018</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O11" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -1352,8 +1394,9 @@
       <c r="N12" s="11">
         <v>2013</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O12" s="11"/>
+    </row>
+    <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
@@ -1396,8 +1439,9 @@
       <c r="N13" s="11">
         <v>2013</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O13" s="11"/>
+    </row>
+    <row r="14" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
@@ -1440,8 +1484,9 @@
       <c r="N14" s="11">
         <v>2013</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O14" s="11"/>
+    </row>
+    <row r="15" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>25</v>
       </c>
@@ -1484,8 +1529,9 @@
       <c r="N15" s="11">
         <v>2013</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O15" s="11"/>
+    </row>
+    <row r="16" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
@@ -1528,8 +1574,9 @@
       <c r="N16" s="11">
         <v>2013</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O16" s="11"/>
+    </row>
+    <row r="17" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>27</v>
       </c>
@@ -1572,8 +1619,9 @@
       <c r="N17" s="11">
         <v>2016</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O17" s="11"/>
+    </row>
+    <row r="18" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>29</v>
       </c>
@@ -1616,8 +1664,9 @@
       <c r="N18" s="11">
         <v>2016</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O18" s="11"/>
+    </row>
+    <row r="19" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>30</v>
       </c>
@@ -1660,8 +1709,9 @@
       <c r="N19" s="11">
         <v>2016</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O19" s="11"/>
+    </row>
+    <row r="20" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>31</v>
       </c>
@@ -1704,8 +1754,9 @@
       <c r="N20" s="11">
         <v>2016</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O20" s="11"/>
+    </row>
+    <row r="21" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
@@ -1748,8 +1799,9 @@
       <c r="N21" s="11">
         <v>2016</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O21" s="11"/>
+    </row>
+    <row r="22" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>35</v>
       </c>
@@ -1792,8 +1844,9 @@
       <c r="N22" s="11">
         <v>2016</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O22" s="11"/>
+    </row>
+    <row r="23" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>36</v>
       </c>
@@ -1836,8 +1889,9 @@
       <c r="N23" s="11">
         <v>2016</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O23" s="11"/>
+    </row>
+    <row r="24" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>37</v>
       </c>
@@ -1880,8 +1934,9 @@
       <c r="N24" s="11">
         <v>2016</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O24" s="11"/>
+    </row>
+    <row r="25" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>39</v>
       </c>
@@ -1924,8 +1979,9 @@
       <c r="N25" s="11">
         <v>2016</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O25" s="11"/>
+    </row>
+    <row r="26" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>42</v>
       </c>
@@ -1968,8 +2024,9 @@
       <c r="N26" s="11">
         <v>2016</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O26" s="11"/>
+    </row>
+    <row r="27" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
         <v>43</v>
       </c>
@@ -2012,8 +2069,11 @@
       <c r="N27" s="8">
         <v>2018</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O27" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="3" t="s">
         <v>44</v>
       </c>
@@ -2056,8 +2116,11 @@
       <c r="N28" s="8">
         <v>2018</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O28" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>45</v>
       </c>
@@ -2100,8 +2163,9 @@
       <c r="N29" s="11">
         <v>2016</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O29" s="11"/>
+    </row>
+    <row r="30" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>46</v>
       </c>
@@ -2144,8 +2208,9 @@
       <c r="N30" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O30" s="11"/>
+    </row>
+    <row r="31" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>47</v>
       </c>
@@ -2188,8 +2253,9 @@
       <c r="N31" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O31" s="11"/>
+    </row>
+    <row r="32" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
@@ -2232,8 +2298,9 @@
       <c r="N32" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O32" s="11"/>
+    </row>
+    <row r="33" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>50</v>
       </c>
@@ -2276,8 +2343,9 @@
       <c r="N33" s="11">
         <v>2016</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O33" s="11"/>
+    </row>
+    <row r="34" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>51</v>
       </c>
@@ -2320,8 +2388,9 @@
       <c r="N34" s="11">
         <v>2016</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O34" s="11"/>
+    </row>
+    <row r="35" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>52</v>
       </c>
@@ -2364,8 +2433,9 @@
       <c r="N35" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O35" s="11"/>
+    </row>
+    <row r="36" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
         <v>53</v>
       </c>
@@ -2408,8 +2478,11 @@
       <c r="N36" s="8">
         <v>2018</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O36" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="s">
         <v>54</v>
       </c>
@@ -2452,8 +2525,11 @@
       <c r="N37" s="8">
         <v>2018</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O37" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
         <v>55</v>
       </c>
@@ -2496,8 +2572,11 @@
       <c r="N38" s="8">
         <v>2018</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O38" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
         <v>58</v>
       </c>
@@ -2540,8 +2619,11 @@
       <c r="N39" s="8">
         <v>2018</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O39" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
         <v>61</v>
       </c>
@@ -2584,8 +2666,11 @@
       <c r="N40" s="8">
         <v>2018</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O40" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
         <v>64</v>
       </c>
@@ -2628,8 +2713,11 @@
       <c r="N41" s="8">
         <v>2018</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O41" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
         <v>66</v>
       </c>
@@ -2672,8 +2760,9 @@
       <c r="N42" s="11">
         <v>2016</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O42" s="11"/>
+    </row>
+    <row r="43" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
         <v>68</v>
       </c>
@@ -2716,8 +2805,9 @@
       <c r="N43" s="11">
         <v>2015</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O43" s="11"/>
+    </row>
+    <row r="44" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>69</v>
       </c>
@@ -2758,8 +2848,9 @@
       <c r="N44" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O44" s="11"/>
+    </row>
+    <row r="45" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>70</v>
       </c>
@@ -2802,8 +2893,9 @@
       <c r="N45" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O45" s="11"/>
+    </row>
+    <row r="46" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>71</v>
       </c>
@@ -2844,8 +2936,9 @@
       <c r="N46" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O46" s="11"/>
+    </row>
+    <row r="47" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
         <v>72</v>
       </c>
@@ -2886,8 +2979,9 @@
       <c r="N47" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O47" s="11"/>
+    </row>
+    <row r="48" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
         <v>73</v>
       </c>
@@ -2930,8 +3024,9 @@
       <c r="N48" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O48" s="11"/>
+    </row>
+    <row r="49" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
         <v>74</v>
       </c>
@@ -2974,8 +3069,9 @@
       <c r="N49" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O49" s="11"/>
+    </row>
+    <row r="50" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
         <v>75</v>
       </c>
@@ -3018,8 +3114,9 @@
       <c r="N50" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O50" s="11"/>
+    </row>
+    <row r="51" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
         <v>76</v>
       </c>
@@ -3062,8 +3159,9 @@
       <c r="N51" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O51" s="11"/>
+    </row>
+    <row r="52" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
         <v>77</v>
       </c>
@@ -3104,8 +3202,9 @@
       <c r="N52" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O52" s="11"/>
+    </row>
+    <row r="53" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
         <v>78</v>
       </c>
@@ -3144,8 +3243,9 @@
       <c r="N53" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O53" s="11"/>
+    </row>
+    <row r="54" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
         <v>79</v>
       </c>
@@ -3184,8 +3284,9 @@
       <c r="N54" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O54" s="11"/>
+    </row>
+    <row r="55" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
         <v>80</v>
       </c>
@@ -3224,8 +3325,9 @@
       <c r="N55" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O55" s="11"/>
+    </row>
+    <row r="56" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
         <v>81</v>
       </c>
@@ -3266,8 +3368,11 @@
       <c r="N56" s="8">
         <v>2018</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O56" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
         <v>82</v>
       </c>
@@ -3310,8 +3415,11 @@
       <c r="N57" s="8">
         <v>2018</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O57" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A58" s="3" t="s">
         <v>84</v>
       </c>
@@ -3354,8 +3462,11 @@
       <c r="N58" s="8">
         <v>2018</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O58" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A59" s="3" t="s">
         <v>86</v>
       </c>
@@ -3398,8 +3509,11 @@
       <c r="N59" s="8">
         <v>2018</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O59" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A60" s="3" t="s">
         <v>87</v>
       </c>
@@ -3440,8 +3554,11 @@
       <c r="N60" s="8">
         <v>2018</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O60" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A61" s="3" t="s">
         <v>88</v>
       </c>
@@ -3480,8 +3597,11 @@
       <c r="N61" s="8">
         <v>2018</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O61" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
         <v>89</v>
       </c>
@@ -3520,8 +3640,9 @@
       <c r="N62" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O62" s="11"/>
+    </row>
+    <row r="63" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
         <v>90</v>
       </c>
@@ -3562,8 +3683,9 @@
       <c r="N63" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O63" s="11"/>
+    </row>
+    <row r="64" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
         <v>91</v>
       </c>
@@ -3604,8 +3726,9 @@
       <c r="N64" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O64" s="11"/>
+    </row>
+    <row r="65" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
         <v>92</v>
       </c>
@@ -3646,8 +3769,9 @@
       <c r="N65" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O65" s="11"/>
+    </row>
+    <row r="66" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
         <v>93</v>
       </c>
@@ -3686,8 +3810,9 @@
       <c r="N66" s="11">
         <v>2013</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O66" s="11"/>
+    </row>
+    <row r="67" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
         <v>94</v>
       </c>
@@ -3728,8 +3853,9 @@
       <c r="N67" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O67" s="11"/>
+    </row>
+    <row r="68" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
         <v>95</v>
       </c>
@@ -3768,8 +3894,9 @@
       <c r="N68" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O68" s="11"/>
+    </row>
+    <row r="69" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
         <v>96</v>
       </c>
@@ -3810,8 +3937,9 @@
       <c r="N69" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O69" s="11"/>
+    </row>
+    <row r="70" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
         <v>97</v>
       </c>
@@ -3850,8 +3978,9 @@
       <c r="N70" s="11">
         <v>2012</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O70" s="11"/>
+    </row>
+    <row r="71" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
         <v>98</v>
       </c>
@@ -3894,8 +4023,9 @@
       <c r="N71" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O71" s="11"/>
+    </row>
+    <row r="72" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
         <v>99</v>
       </c>
@@ -3938,8 +4068,9 @@
       <c r="N72" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O72" s="11"/>
+    </row>
+    <row r="73" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
         <v>100</v>
       </c>
@@ -3980,8 +4111,9 @@
       <c r="N73" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O73" s="11"/>
+    </row>
+    <row r="74" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
         <v>101</v>
       </c>
@@ -4022,8 +4154,9 @@
       <c r="N74" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O74" s="11"/>
+    </row>
+    <row r="75" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
         <v>102</v>
       </c>
@@ -4064,8 +4197,9 @@
       <c r="N75" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O75" s="11"/>
+    </row>
+    <row r="76" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
         <v>103</v>
       </c>
@@ -4106,8 +4240,9 @@
       <c r="N76" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O76" s="11"/>
+    </row>
+    <row r="77" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
         <v>104</v>
       </c>
@@ -4148,8 +4283,9 @@
       <c r="N77" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O77" s="11"/>
+    </row>
+    <row r="78" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
         <v>105</v>
       </c>
@@ -4190,8 +4326,9 @@
       <c r="N78" s="11">
         <v>2013</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O78" s="11"/>
+    </row>
+    <row r="79" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
         <v>106</v>
       </c>
@@ -4232,8 +4369,9 @@
       <c r="N79" s="11">
         <v>2013</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O79" s="11"/>
+    </row>
+    <row r="80" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
         <v>107</v>
       </c>
@@ -4250,7 +4388,7 @@
         <v>0.04</v>
       </c>
       <c r="F80" s="12">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G80" s="12">
         <v>13.9</v>
@@ -4274,8 +4412,12 @@
       <c r="N80" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O80" s="11"/>
+      <c r="P80" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
         <v>108</v>
       </c>
@@ -4316,8 +4458,9 @@
       <c r="N81" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O81" s="11"/>
+    </row>
+    <row r="82" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
         <v>109</v>
       </c>
@@ -4358,8 +4501,9 @@
       <c r="N82" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O82" s="11"/>
+    </row>
+    <row r="83" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
         <v>110</v>
       </c>
@@ -4400,8 +4544,9 @@
       <c r="N83" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="84" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O83" s="11"/>
+    </row>
+    <row r="84" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
         <v>111</v>
       </c>
@@ -4442,8 +4587,9 @@
       <c r="N84" s="11">
         <v>2017</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O84" s="11"/>
+    </row>
+    <row r="85" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
         <v>112</v>
       </c>
@@ -4484,8 +4630,9 @@
       <c r="N85" s="11">
         <v>2013</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O85" s="11"/>
+    </row>
+    <row r="86" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
         <v>113</v>
       </c>
@@ -4528,8 +4675,9 @@
       <c r="N86" s="11">
         <v>2009</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O86" s="11"/>
+    </row>
+    <row r="87" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
         <v>114</v>
       </c>
@@ -4572,8 +4720,9 @@
       <c r="N87" s="11">
         <v>2008</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" ht="15" x14ac:dyDescent="0.15">
+      <c r="O87" s="11"/>
+    </row>
+    <row r="88" spans="1:15" ht="15" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
         <v>115</v>
       </c>
@@ -4616,9 +4765,9 @@
       <c r="N88" s="11">
         <v>2008</v>
       </c>
+      <c r="O88" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N88" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>